--- a/factor_build/outputs/03_regression_results.xlsx
+++ b/factor_build/outputs/03_regression_results.xlsx
@@ -486,19 +486,19 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0113</v>
+        <v>0.0187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6834075690334243</v>
+        <v>0.4750896761418777</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0113</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="3">
@@ -516,19 +516,19 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1275</v>
+        <v>-0.0833</v>
       </c>
       <c r="F3" t="n">
-        <v>4.002130915061709e-06</v>
+        <v>0.001453459014690324</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0163</v>
+        <v>0.0069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1275</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="4">
@@ -546,19 +546,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1299</v>
+        <v>1459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0588</v>
+        <v>0.0393</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03396974467401923</v>
+        <v>0.133733104636454</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0035</v>
+        <v>0.0015</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0588</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="5">
@@ -576,19 +576,19 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1298</v>
+        <v>1458</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0377</v>
+        <v>-0.0227</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1746535481031436</v>
+        <v>0.3869148351399843</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0014</v>
+        <v>0.0005</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0377</v>
+        <v>0.0227</v>
       </c>
     </row>
     <row r="6">
@@ -606,19 +606,19 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0161</v>
+        <v>-0.0108</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6057833617000412</v>
+        <v>0.7104562231549213</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0161</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="7">
@@ -636,19 +636,19 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1031</v>
+        <v>1191</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0347</v>
+        <v>0.0113</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2662940407180996</v>
+        <v>0.6956971967775233</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0012</v>
+        <v>0.0001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0347</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="8">
@@ -666,19 +666,19 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1030</v>
+        <v>1190</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0323</v>
+        <v>0.0145</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3000629850173451</v>
+        <v>0.6173669995779332</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0323</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="9">
@@ -696,19 +696,19 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1029</v>
+        <v>1189</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0199</v>
+        <v>-0.0124</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5239099929849655</v>
+        <v>0.669539503579381</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004</v>
+        <v>0.0002</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0199</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="10">
@@ -726,19 +726,19 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0049</v>
+        <v>0.0044</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8494285022801692</v>
+        <v>0.8582327395521049</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0049</v>
+        <v>0.0044</v>
       </c>
     </row>
     <row r="11">
@@ -756,19 +756,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0148</v>
+        <v>0.0103</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5682251964419794</v>
+        <v>0.677724089718272</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0148</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="12">
@@ -786,19 +786,19 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0298</v>
+        <v>-0.0276</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2507162135737326</v>
+        <v>0.2639333844753816</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0009</v>
+        <v>0.0008</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0298</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="13">
@@ -816,19 +816,19 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0027</v>
+        <v>0.0022</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9165339116765489</v>
+        <v>0.9295236903320646</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0027</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="14">
@@ -846,19 +846,19 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1304</v>
+        <v>1464</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0067</v>
+        <v>-0.0115</v>
       </c>
       <c r="F14" t="n">
-        <v>0.808564067894796</v>
+        <v>0.6597160287940732</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0067</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="15">
@@ -876,19 +876,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1303</v>
+        <v>1463</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0223</v>
+        <v>0.0176</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4219322145084275</v>
+        <v>0.5017349834685116</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0005</v>
+        <v>0.0003</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0223</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="16">
@@ -906,19 +906,19 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0408</v>
+        <v>0.0137</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1408149754827832</v>
+        <v>0.6017548190569371</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0017</v>
+        <v>0.0002</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0408</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="17">
@@ -936,19 +936,19 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0578</v>
+        <v>-0.0525</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03696788601635918</v>
+        <v>0.04480930104797084</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0033</v>
+        <v>0.0028</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0578</v>
+        <v>0.0525</v>
       </c>
     </row>
     <row r="18">
@@ -966,19 +966,19 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1319</v>
+        <v>1479</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.005</v>
+        <v>-0.0012</v>
       </c>
       <c r="F18" t="n">
-        <v>0.855776843162099</v>
+        <v>0.9621404497812674</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.005</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="19">
@@ -996,19 +996,19 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1318</v>
+        <v>1478</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0089</v>
+        <v>0.0069</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7462110514453609</v>
+        <v>0.7902424191695985</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0089</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="20">
@@ -1026,19 +1026,19 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>1317</v>
+        <v>1477</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0016</v>
+        <v>0.0327</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9544784785964918</v>
+        <v>0.2090117117928963</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0016</v>
+        <v>0.0327</v>
       </c>
     </row>
     <row r="21">
@@ -1056,19 +1056,19 @@
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>1316</v>
+        <v>1476</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0064</v>
+        <v>0.0274</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8178920887923266</v>
+        <v>0.2922536312164267</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0064</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="22">
@@ -1086,19 +1086,19 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1062</v>
+        <v>1217</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0584</v>
+        <v>-0.0362</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05716721949898971</v>
+        <v>0.2068492918188305</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0034</v>
+        <v>0.0013</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0584</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="23">
@@ -1116,19 +1116,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1061</v>
+        <v>1216</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0572</v>
+        <v>-0.0372</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06254188892485206</v>
+        <v>0.1949472017963964</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0033</v>
+        <v>0.0014</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0572</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="24">
@@ -1146,19 +1146,19 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>1060</v>
+        <v>1215</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0491</v>
+        <v>-0.0311</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1103481200953223</v>
+        <v>0.2792213091759292</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0024</v>
+        <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0491</v>
+        <v>0.0311</v>
       </c>
     </row>
     <row r="25">
@@ -1176,19 +1176,19 @@
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>1059</v>
+        <v>1214</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0452</v>
+        <v>-0.0053</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1416798322023862</v>
+        <v>0.8542571162674857</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0452</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="26">
@@ -1206,19 +1206,19 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0441</v>
+        <v>0.0104</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08911143776518202</v>
+        <v>0.6727430910349623</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0019</v>
+        <v>0.0001</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0441</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="27">
@@ -1236,19 +1236,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0421</v>
+        <v>0.0131</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1052042130303072</v>
+        <v>0.5966852115342544</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0018</v>
+        <v>0.0002</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0421</v>
+        <v>0.0131</v>
       </c>
     </row>
     <row r="28">
@@ -1266,19 +1266,19 @@
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0414</v>
+        <v>0.0214</v>
       </c>
       <c r="F28" t="n">
-        <v>0.110684627741393</v>
+        <v>0.3863928349370168</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0017</v>
+        <v>0.0005</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0414</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="29">
@@ -1296,19 +1296,19 @@
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0495</v>
+        <v>0.021</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05686563044015062</v>
+        <v>0.3939857679662989</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0495</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="30">
@@ -1326,19 +1326,19 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1315</v>
+        <v>1475</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0176</v>
+        <v>-0.003</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5244092983884787</v>
+        <v>0.9091205148785386</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0176</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="31">
@@ -1356,19 +1356,19 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1314</v>
+        <v>1474</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0348</v>
+        <v>-0.0507</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2071451005166191</v>
+        <v>0.05167641460247162</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0012</v>
+        <v>0.0026</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0348</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="32">
@@ -1386,19 +1386,19 @@
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>1313</v>
+        <v>1473</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0355</v>
+        <v>-0.0527</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1988918731389992</v>
+        <v>0.04300037084029729</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0013</v>
+        <v>0.0028</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0355</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="33">
@@ -1416,19 +1416,19 @@
         <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>1312</v>
+        <v>1472</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0412</v>
+        <v>-0.0508</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1354206078635581</v>
+        <v>0.05147237372183522</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0017</v>
+        <v>0.0026</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0412</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="34">
@@ -1446,19 +1446,19 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E34" t="n">
-        <v>0.015</v>
+        <v>-0.0173</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5875148133112738</v>
+        <v>0.5092517581144104</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="H34" t="n">
-        <v>0.015</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="35">
@@ -1476,19 +1476,19 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0332</v>
+        <v>-0.0562</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2311245244705381</v>
+        <v>0.03179241750970469</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0011</v>
+        <v>0.0032</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0332</v>
+        <v>0.0562</v>
       </c>
     </row>
     <row r="36">
@@ -1506,19 +1506,19 @@
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0102</v>
+        <v>-0.0007</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7133086026734845</v>
+        <v>0.9782259121212434</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0102</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="37">
@@ -1536,19 +1536,19 @@
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>1299</v>
+        <v>1459</v>
       </c>
       <c r="E37" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0004</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7761668978795833</v>
+        <v>0.9884065617972515</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="38">
@@ -1566,19 +1566,19 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0578</v>
+        <v>0.0445</v>
       </c>
       <c r="F38" t="n">
-        <v>0.06329825959850663</v>
+        <v>0.124648273891981</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0033</v>
+        <v>0.002</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0578</v>
+        <v>0.0445</v>
       </c>
     </row>
     <row r="39">
@@ -1596,19 +1596,19 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0495</v>
+        <v>-0.0344</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1116891840262111</v>
+        <v>0.2351869228599912</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0025</v>
+        <v>0.0012</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0495</v>
+        <v>0.0344</v>
       </c>
     </row>
     <row r="40">
@@ -1626,19 +1626,19 @@
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>1031</v>
+        <v>1191</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.0664</v>
+        <v>-0.0297</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0329387044269339</v>
+        <v>0.3050087051937888</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0044</v>
+        <v>0.0009</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0664</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="41">
@@ -1656,19 +1656,19 @@
         <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>1030</v>
+        <v>1190</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0005</v>
+        <v>0.0601</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9882646835840111</v>
+        <v>0.03807197236771273</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.0036</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0005</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="42">
@@ -1686,19 +1686,19 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.0616</v>
+        <v>-0.0251</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01758938509015766</v>
+        <v>0.3089443873122342</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0038</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0616</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="43">
@@ -1716,19 +1716,19 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.0178</v>
+        <v>-0.0072</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4936406032526651</v>
+        <v>0.7714292889831671</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0178</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="44">
@@ -1746,19 +1746,19 @@
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0209</v>
+        <v>-0.0032</v>
       </c>
       <c r="F44" t="n">
-        <v>0.421671951073284</v>
+        <v>0.8967421790374701</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0209</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="45">
@@ -1776,19 +1776,19 @@
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0376</v>
+        <v>0.0203</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1480312971281428</v>
+        <v>0.410832570541075</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0014</v>
+        <v>0.0004</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0376</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="46">
@@ -1806,19 +1806,19 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1305</v>
+        <v>1465</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0246</v>
+        <v>0.0658</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3743205009471464</v>
+        <v>0.01182197363890306</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0246</v>
+        <v>0.0658</v>
       </c>
     </row>
     <row r="47">
@@ -1836,19 +1836,19 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1304</v>
+        <v>1464</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0119</v>
       </c>
       <c r="F47" t="n">
-        <v>0.005542304151129953</v>
+        <v>0.648998076975998</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0059</v>
+        <v>0.0001</v>
       </c>
       <c r="H47" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="48">
@@ -1866,19 +1866,19 @@
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>1303</v>
+        <v>1463</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0706</v>
+        <v>-0.0251</v>
       </c>
       <c r="F48" t="n">
-        <v>0.01082749214576983</v>
+        <v>0.3377396419284364</v>
       </c>
       <c r="G48" t="n">
-        <v>0.005</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0706</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="49">
@@ -1896,19 +1896,19 @@
         <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0012</v>
       </c>
       <c r="F49" t="n">
-        <v>0.01713703726938595</v>
+        <v>0.9620602781232176</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0044</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="50">
@@ -1926,19 +1926,19 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1857</v>
+        <v>0.197</v>
       </c>
       <c r="F50" t="n">
-        <v>1.462278934836283e-11</v>
+        <v>2.975956023165638e-14</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0345</v>
+        <v>0.0388</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1857</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="51">
@@ -1956,19 +1956,19 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0806</v>
+        <v>-0.0244</v>
       </c>
       <c r="F51" t="n">
-        <v>0.003633692135525864</v>
+        <v>0.3510963880959489</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0065</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0806</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="52">
@@ -1986,19 +1986,19 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0286</v>
+        <v>0.0118</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3022359816743809</v>
+        <v>0.6527119250524643</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0008</v>
+        <v>0.0001</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0286</v>
+        <v>0.0118</v>
       </c>
     </row>
     <row r="53">
@@ -2016,19 +2016,19 @@
         <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>1299</v>
+        <v>1459</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0369</v>
+        <v>-0.0117</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1837689902904799</v>
+        <v>0.6540668894370165</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0014</v>
+        <v>0.0001</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0369</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="54">
@@ -2046,19 +2046,19 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0009</v>
+        <v>-0.0355</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9771344928513677</v>
+        <v>0.219927083992585</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0009</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="55">
@@ -2076,19 +2076,19 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0025</v>
+        <v>-0.0261</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9352542479989596</v>
+        <v>0.3687488053100063</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0025</v>
+        <v>0.0261</v>
       </c>
     </row>
     <row r="56">
@@ -2106,19 +2106,19 @@
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>1031</v>
+        <v>1191</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0649</v>
+        <v>-0.0059</v>
       </c>
       <c r="F56" t="n">
-        <v>0.03726009446297148</v>
+        <v>0.8393897880429865</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0042</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0649</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="57">
@@ -2136,19 +2136,19 @@
         <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>1030</v>
+        <v>1190</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0144</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6451009738741281</v>
+        <v>0.771474447699564</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0144</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2166,19 +2166,19 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.06</v>
+        <v>-0.0745</v>
       </c>
       <c r="F58" t="n">
-        <v>0.02068301455114766</v>
+        <v>0.002476983822716446</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0036</v>
+        <v>0.0056</v>
       </c>
       <c r="H58" t="n">
-        <v>0.06</v>
+        <v>0.0745</v>
       </c>
     </row>
     <row r="59">
@@ -2196,19 +2196,19 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0078</v>
+        <v>-0.0209</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7651163999285717</v>
+        <v>0.3977101395973149</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0001</v>
+        <v>0.0004</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0078</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="60">
@@ -2226,19 +2226,19 @@
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E60" t="n">
-        <v>0.002</v>
+        <v>-0.0168</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9393779420315851</v>
+        <v>0.4958885259213262</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="H60" t="n">
-        <v>0.002</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="61">
@@ -2256,19 +2256,19 @@
         <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.0066</v>
+        <v>0.0101</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7981061838296901</v>
+        <v>0.6837282141712854</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0066</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="62">
@@ -2286,19 +2286,19 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>1305</v>
+        <v>1465</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0355</v>
+        <v>-0.0775</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2001503494200941</v>
+        <v>0.003004213155374892</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0013</v>
+        <v>0.006</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0355</v>
+        <v>0.0775</v>
       </c>
     </row>
     <row r="63">
@@ -2316,19 +2316,19 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>1304</v>
+        <v>1464</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0339</v>
+        <v>-0.0238</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2214716653910629</v>
+        <v>0.3629921999110471</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0011</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0339</v>
+        <v>0.0238</v>
       </c>
     </row>
     <row r="64">
@@ -2346,19 +2346,19 @@
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>1303</v>
+        <v>1463</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0283</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.307432833266031</v>
+        <v>0.9998686205469801</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0008</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2376,19 +2376,19 @@
         <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0319</v>
+        <v>-0.037</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2498934444710897</v>
+        <v>0.1570616985539672</v>
       </c>
       <c r="G65" t="n">
-        <v>0.001</v>
+        <v>0.0014</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0319</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="66">
@@ -2406,19 +2406,19 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.0206</v>
+        <v>-0.0233</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4566944708847293</v>
+        <v>0.3729089728801068</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0004</v>
+        <v>0.0005</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0206</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="67">
@@ -2436,19 +2436,19 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.0224</v>
+        <v>-0.0318</v>
       </c>
       <c r="F67" t="n">
-        <v>0.420172941575884</v>
+        <v>0.2247883413685239</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0224</v>
+        <v>0.0318</v>
       </c>
     </row>
     <row r="68">
@@ -2466,19 +2466,19 @@
         <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.0189</v>
+        <v>-0.0386</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4948557470141868</v>
+        <v>0.140052577372241</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0004</v>
+        <v>0.0015</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0189</v>
+        <v>0.0386</v>
       </c>
     </row>
     <row r="69">
@@ -2496,19 +2496,19 @@
         <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>1299</v>
+        <v>1459</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.023</v>
+        <v>-0.0396</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4074016734720176</v>
+        <v>0.1303327224313007</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0005</v>
+        <v>0.0016</v>
       </c>
       <c r="H69" t="n">
-        <v>0.023</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="70">
@@ -2526,19 +2526,19 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.0183</v>
+        <v>0.0187</v>
       </c>
       <c r="F70" t="n">
-        <v>0.5563967776727436</v>
+        <v>0.5191251215378676</v>
       </c>
       <c r="G70" t="n">
         <v>0.0003</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0183</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="71">
@@ -2556,19 +2556,19 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0208</v>
+        <v>0.0373</v>
       </c>
       <c r="F71" t="n">
-        <v>0.5042552568512636</v>
+        <v>0.1985985024949125</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0004</v>
+        <v>0.0014</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0208</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="72">
@@ -2586,19 +2586,19 @@
         <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>1031</v>
+        <v>1191</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.008</v>
+        <v>0.0212</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7982112781882216</v>
+        <v>0.4643278454205312</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0001</v>
+        <v>0.0005</v>
       </c>
       <c r="H72" t="n">
-        <v>0.008</v>
+        <v>0.0212</v>
       </c>
     </row>
     <row r="73">
@@ -2616,19 +2616,19 @@
         <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>1030</v>
+        <v>1190</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0188</v>
+        <v>0.0041</v>
       </c>
       <c r="F73" t="n">
-        <v>0.5466939288238503</v>
+        <v>0.8882555748640895</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0188</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="74">
@@ -2646,19 +2646,19 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E74" t="n">
-        <v>0.1034</v>
+        <v>0.049</v>
       </c>
       <c r="F74" t="n">
-        <v>6.525116086013564e-05</v>
+        <v>0.04683192060403791</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0107</v>
+        <v>0.0024</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1034</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="75">
@@ -2676,19 +2676,19 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0277</v>
+        <v>-0.0132</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2868519812064371</v>
+        <v>0.5935808211739825</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0008</v>
+        <v>0.0002</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0277</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="76">
@@ -2706,19 +2706,19 @@
         <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0049</v>
+        <v>-0.0312</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8505250907040041</v>
+        <v>0.2053743533507866</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0049</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="77">
@@ -2736,19 +2736,19 @@
         <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.0185</v>
+        <v>-0.0323</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4755529703450156</v>
+        <v>0.1906180709379581</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0003</v>
+        <v>0.001</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0185</v>
+        <v>0.0323</v>
       </c>
     </row>
     <row r="78">
@@ -2766,19 +2766,19 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>1305</v>
+        <v>1465</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0025</v>
+        <v>-0.0252</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9273515526570381</v>
+        <v>0.3356431948219</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0025</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="79">
@@ -2796,19 +2796,19 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>1304</v>
+        <v>1464</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0042</v>
+        <v>-0.011</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8802183160551784</v>
+        <v>0.6727316782460798</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0042</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="80">
@@ -2826,19 +2826,19 @@
         <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>1303</v>
+        <v>1463</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0113</v>
+        <v>-0.0018</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6846276614202284</v>
+        <v>0.9443697180826229</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0113</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="81">
@@ -2856,19 +2856,19 @@
         <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0159</v>
+        <v>0.0089</v>
       </c>
       <c r="F81" t="n">
-        <v>0.5663704358007461</v>
+        <v>0.7347296806616865</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0159</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="82">
@@ -2886,19 +2886,19 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0389</v>
+        <v>0.0377</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1606387937452214</v>
+        <v>0.1501485677933019</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0015</v>
+        <v>0.0014</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0389</v>
+        <v>0.0377</v>
       </c>
     </row>
     <row r="83">
@@ -2916,19 +2916,19 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.0202</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F83" t="n">
-        <v>0.4665596747839348</v>
+        <v>0.7234569226164193</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0202</v>
+        <v>0.009299999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -2946,19 +2946,19 @@
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="E84" t="n">
-        <v>0.023</v>
+        <v>0.0302</v>
       </c>
       <c r="F84" t="n">
-        <v>0.4079001193534161</v>
+        <v>0.2485070930078257</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="H84" t="n">
-        <v>0.023</v>
+        <v>0.0302</v>
       </c>
     </row>
     <row r="85">
@@ -2976,19 +2976,19 @@
         <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>1299</v>
+        <v>1459</v>
       </c>
       <c r="E85" t="n">
-        <v>0.0048</v>
+        <v>0.0302</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8622707940672132</v>
+        <v>0.2485810753679044</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0048</v>
+        <v>0.0302</v>
       </c>
     </row>
     <row r="86">
@@ -3006,19 +3006,19 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1003</v>
+        <v>0.0835</v>
       </c>
       <c r="F86" t="n">
-        <v>0.001244884131618857</v>
+        <v>0.003909283436569167</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0101</v>
+        <v>0.007</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1003</v>
+        <v>0.0835</v>
       </c>
     </row>
     <row r="87">
@@ -3036,19 +3036,19 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0064</v>
+        <v>0.0299</v>
       </c>
       <c r="F87" t="n">
-        <v>0.8378372763778323</v>
+        <v>0.3029698003597812</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0064</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="88">
@@ -3066,19 +3066,19 @@
         <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>1031</v>
+        <v>1191</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.0308</v>
+        <v>-0.0148</v>
       </c>
       <c r="F88" t="n">
-        <v>0.3238609986681283</v>
+        <v>0.6105810789055173</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0009</v>
+        <v>0.0002</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0308</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="89">
@@ -3096,19 +3096,19 @@
         <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>1030</v>
+        <v>1190</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.0267</v>
+        <v>-0.0169</v>
       </c>
       <c r="F89" t="n">
-        <v>0.391216614043275</v>
+        <v>0.5599273184326377</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0007</v>
+        <v>0.0003</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0267</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="90">
@@ -3126,19 +3126,19 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.0114</v>
+        <v>-0.0379</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6599139907737651</v>
+        <v>0.123945590611027</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0001</v>
+        <v>0.0014</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0114</v>
+        <v>0.0379</v>
       </c>
     </row>
     <row r="91">
@@ -3156,19 +3156,19 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0073</v>
+        <v>0.0062</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7781712334169522</v>
+        <v>0.8022660236696634</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0073</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="92">
@@ -3186,19 +3186,19 @@
         <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.0353</v>
+        <v>-0.0238</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1741413831980601</v>
+        <v>0.3349503069673893</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0012</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0353</v>
+        <v>0.0238</v>
       </c>
     </row>
     <row r="93">
@@ -3216,19 +3216,19 @@
         <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.0386</v>
+        <v>-0.0141</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1370412296198306</v>
+        <v>0.5686174391365877</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0015</v>
+        <v>0.0002</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0386</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="94">
@@ -3246,19 +3246,19 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>1305</v>
+        <v>1465</v>
       </c>
       <c r="E94" t="n">
-        <v>0.0176</v>
+        <v>0.0032</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5255060243407867</v>
+        <v>0.901589843073422</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0176</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="95">
@@ -3276,19 +3276,19 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1304</v>
+        <v>1464</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.0193</v>
+        <v>-0.0167</v>
       </c>
       <c r="F95" t="n">
-        <v>0.4872523131558449</v>
+        <v>0.5219725167920005</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0193</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="96">
@@ -3306,19 +3306,19 @@
         <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>1303</v>
+        <v>1463</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.0204</v>
+        <v>-0.0289</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4613846702106932</v>
+        <v>0.268531892436763</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0204</v>
+        <v>0.0289</v>
       </c>
     </row>
     <row r="97">
@@ -3336,19 +3336,19 @@
         <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.033</v>
+        <v>-0.0308</v>
       </c>
       <c r="F97" t="n">
-        <v>0.2334362542138325</v>
+        <v>0.2389472317155701</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0011</v>
+        <v>0.0009</v>
       </c>
       <c r="H97" t="n">
-        <v>0.033</v>
+        <v>0.0308</v>
       </c>
     </row>
     <row r="98">
@@ -3366,19 +3366,19 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0172</v>
+        <v>0.0371</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5353629006745996</v>
+        <v>0.1557906961711858</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0003</v>
+        <v>0.0014</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0172</v>
+        <v>0.0371</v>
       </c>
     </row>
     <row r="99">
@@ -3396,19 +3396,19 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.0348</v>
+        <v>0.0075</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2101238980683106</v>
+        <v>0.7747950640597497</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0012</v>
+        <v>0.0001</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0348</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="100">
@@ -3426,19 +3426,19 @@
         <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0202</v>
+        <v>0.0287</v>
       </c>
       <c r="F100" t="n">
-        <v>0.4669149255346633</v>
+        <v>0.273916039250704</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0202</v>
+        <v>0.0287</v>
       </c>
     </row>
     <row r="101">
@@ -3456,19 +3456,19 @@
         <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>1299</v>
+        <v>1459</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0327</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7761993021529299</v>
+        <v>0.2113846132384784</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0001</v>
+        <v>0.0011</v>
       </c>
       <c r="H101" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0327</v>
       </c>
     </row>
     <row r="102">
@@ -3486,19 +3486,19 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0974</v>
+        <v>0.0795</v>
       </c>
       <c r="F102" t="n">
-        <v>0.001725477739666054</v>
+        <v>0.005986226028564703</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0095</v>
+        <v>0.0063</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0974</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="103">
@@ -3516,19 +3516,19 @@
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.0033</v>
+        <v>0.0235</v>
       </c>
       <c r="F103" t="n">
-        <v>0.91482123212237</v>
+        <v>0.4179096721577419</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0033</v>
+        <v>0.0235</v>
       </c>
     </row>
     <row r="104">
@@ -3546,19 +3546,19 @@
         <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>1031</v>
+        <v>1191</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.0297</v>
+        <v>-0.0215</v>
       </c>
       <c r="F104" t="n">
-        <v>0.341306911645309</v>
+        <v>0.4593588013945522</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0297</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="105">
@@ -3576,19 +3576,19 @@
         <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>1030</v>
+        <v>1190</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.0228</v>
+        <v>-0.024</v>
       </c>
       <c r="F105" t="n">
-        <v>0.4652971953724416</v>
+        <v>0.4074667728767247</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0005</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0228</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="106">
@@ -3606,19 +3606,19 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.0143</v>
+        <v>-0.0376</v>
       </c>
       <c r="F106" t="n">
-        <v>0.5830377227536123</v>
+        <v>0.1276497656069074</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0002</v>
+        <v>0.0014</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0143</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="107">
@@ -3636,19 +3636,19 @@
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9990135255704835</v>
+        <v>0.824161411605097</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="108">
@@ -3666,19 +3666,19 @@
         <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.0286</v>
+        <v>-0.0224</v>
       </c>
       <c r="F108" t="n">
-        <v>0.2716181636085787</v>
+        <v>0.3649963532889636</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0008</v>
+        <v>0.0005</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0286</v>
+        <v>0.0224</v>
       </c>
     </row>
     <row r="109">
@@ -3696,19 +3696,19 @@
         <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.0342</v>
+        <v>-0.0136</v>
       </c>
       <c r="F109" t="n">
-        <v>0.18775676629118</v>
+        <v>0.5803584977300813</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0012</v>
+        <v>0.0002</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0342</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="110">
@@ -3726,19 +3726,19 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>1305</v>
+        <v>1465</v>
       </c>
       <c r="E110" t="n">
-        <v>0.0155</v>
+        <v>0.0052</v>
       </c>
       <c r="F110" t="n">
-        <v>0.5762478050354469</v>
+        <v>0.8422018941172228</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0155</v>
+        <v>0.0052</v>
       </c>
     </row>
     <row r="111">
@@ -3756,19 +3756,19 @@
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>1304</v>
+        <v>1464</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.034</v>
+        <v>-0.0172</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2204935147191239</v>
+        <v>0.5105542348076552</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0012</v>
+        <v>0.0003</v>
       </c>
       <c r="H111" t="n">
-        <v>0.034</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="112">
@@ -3786,19 +3786,19 @@
         <v>2</v>
       </c>
       <c r="D112" t="n">
-        <v>1303</v>
+        <v>1463</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.0225</v>
+        <v>-0.0295</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4169879033983061</v>
+        <v>0.2600958142696354</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0225</v>
+        <v>0.0295</v>
       </c>
     </row>
     <row r="113">
@@ -3816,19 +3816,19 @@
         <v>3</v>
       </c>
       <c r="D113" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.0394</v>
+        <v>-0.0356</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1551322912485434</v>
+        <v>0.1733360130595729</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0016</v>
+        <v>0.0013</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0394</v>
+        <v>0.0356</v>
       </c>
     </row>
     <row r="114">
@@ -3846,19 +3846,19 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0181</v>
+        <v>0.039</v>
       </c>
       <c r="F114" t="n">
-        <v>0.5140431790554723</v>
+        <v>0.136295597742238</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0003</v>
+        <v>0.0015</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0181</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="115">
@@ -3876,19 +3876,19 @@
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.0361</v>
+        <v>0.0072</v>
       </c>
       <c r="F115" t="n">
-        <v>0.1937642673149681</v>
+        <v>0.7832134224459452</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0013</v>
+        <v>0.0001</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0361</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="116">
@@ -3906,19 +3906,19 @@
         <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0218</v>
+        <v>0.0311</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4314310433737426</v>
+        <v>0.2349793786392783</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0218</v>
+        <v>0.0311</v>
       </c>
     </row>
     <row r="117">
@@ -3936,19 +3936,19 @@
         <v>3</v>
       </c>
       <c r="D117" t="n">
-        <v>1299</v>
+        <v>1459</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.0108</v>
+        <v>0.0308</v>
       </c>
       <c r="F117" t="n">
-        <v>0.6961880173773268</v>
+        <v>0.239194004246513</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0001</v>
+        <v>0.001</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0108</v>
+        <v>0.0308</v>
       </c>
     </row>
     <row r="118">
@@ -3966,19 +3966,19 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E118" t="n">
-        <v>0.097</v>
+        <v>0.0791</v>
       </c>
       <c r="F118" t="n">
-        <v>0.001798779041004703</v>
+        <v>0.006260604829910568</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0094</v>
+        <v>0.0063</v>
       </c>
       <c r="H118" t="n">
-        <v>0.097</v>
+        <v>0.0791</v>
       </c>
     </row>
     <row r="119">
@@ -3996,19 +3996,19 @@
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.0033</v>
+        <v>0.0232</v>
       </c>
       <c r="F119" t="n">
-        <v>0.9155258191597705</v>
+        <v>0.4228694000929897</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0033</v>
+        <v>0.0232</v>
       </c>
     </row>
     <row r="120">
@@ -4026,19 +4026,19 @@
         <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>1031</v>
+        <v>1191</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.0296</v>
+        <v>-0.0214</v>
       </c>
       <c r="F120" t="n">
-        <v>0.3416217601655591</v>
+        <v>0.4615125326424407</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0296</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="121">
@@ -4056,19 +4056,19 @@
         <v>3</v>
       </c>
       <c r="D121" t="n">
-        <v>1030</v>
+        <v>1190</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.0221</v>
+        <v>-0.0231</v>
       </c>
       <c r="F121" t="n">
-        <v>0.4794536429646243</v>
+        <v>0.4256778107570225</v>
       </c>
       <c r="G121" t="n">
         <v>0.0005</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0221</v>
+        <v>0.0231</v>
       </c>
     </row>
     <row r="122">
@@ -4086,19 +4086,19 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.0148</v>
+        <v>-0.0361</v>
       </c>
       <c r="F122" t="n">
-        <v>0.5677460578955824</v>
+        <v>0.142772465861559</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0002</v>
+        <v>0.0013</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0148</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="123">
@@ -4116,19 +4116,19 @@
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.0012</v>
+        <v>0.0069</v>
       </c>
       <c r="F123" t="n">
-        <v>0.962855505938551</v>
+        <v>0.7788639458067261</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0012</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="124">
@@ -4146,19 +4146,19 @@
         <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.0367</v>
+        <v>-0.0232</v>
       </c>
       <c r="F124" t="n">
-        <v>0.1577792206667341</v>
+        <v>0.3470644184315337</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0013</v>
+        <v>0.0005</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0367</v>
+        <v>0.0232</v>
       </c>
     </row>
     <row r="125">
@@ -4176,19 +4176,19 @@
         <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.0393</v>
+        <v>-0.0138</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1301886878886084</v>
+        <v>0.575024359431512</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0015</v>
+        <v>0.0002</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0393</v>
+        <v>0.0138</v>
       </c>
     </row>
     <row r="126">
@@ -4206,19 +4206,19 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>1305</v>
+        <v>1465</v>
       </c>
       <c r="E126" t="n">
-        <v>0.0144</v>
+        <v>0.0056</v>
       </c>
       <c r="F126" t="n">
-        <v>0.602592732575041</v>
+        <v>0.8300531253474358</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0144</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="127">
@@ -4236,19 +4236,19 @@
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>1304</v>
+        <v>1464</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.0363</v>
+        <v>-0.017</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1896354987823763</v>
+        <v>0.5147449779438634</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0013</v>
+        <v>0.0003</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0363</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="128">
@@ -4266,19 +4266,19 @@
         <v>2</v>
       </c>
       <c r="D128" t="n">
-        <v>1303</v>
+        <v>1463</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.0258</v>
+        <v>-0.0293</v>
       </c>
       <c r="F128" t="n">
-        <v>0.3517236071467979</v>
+        <v>0.2622342844937536</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0258</v>
+        <v>0.0293</v>
       </c>
     </row>
     <row r="129">
@@ -4296,19 +4296,19 @@
         <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.042</v>
+        <v>-0.0353</v>
       </c>
       <c r="F129" t="n">
-        <v>0.129652809036175</v>
+        <v>0.1775366575291561</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0018</v>
+        <v>0.0012</v>
       </c>
       <c r="H129" t="n">
-        <v>0.042</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="130">
@@ -4326,19 +4326,19 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E130" t="n">
-        <v>0.0295</v>
+        <v>0.0405</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2872950724106819</v>
+        <v>0.1217201000498882</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0009</v>
+        <v>0.0016</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0295</v>
+        <v>0.0405</v>
       </c>
     </row>
     <row r="131">
@@ -4356,19 +4356,19 @@
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.0342</v>
+        <v>0.0098</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2172257506920097</v>
+        <v>0.7090444298049667</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0012</v>
+        <v>0.0001</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0342</v>
+        <v>0.0098</v>
       </c>
     </row>
     <row r="132">
@@ -4386,19 +4386,19 @@
         <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0163</v>
+        <v>0.0336</v>
       </c>
       <c r="F132" t="n">
-        <v>0.557263464495108</v>
+        <v>0.1998882552034283</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0003</v>
+        <v>0.0011</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0163</v>
+        <v>0.0336</v>
       </c>
     </row>
     <row r="133">
@@ -4416,19 +4416,19 @@
         <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>1299</v>
+        <v>1459</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.0174</v>
+        <v>0.0355</v>
       </c>
       <c r="F133" t="n">
-        <v>0.5310291853156268</v>
+        <v>0.175855032966838</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0003</v>
+        <v>0.0013</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0174</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="134">
@@ -4446,19 +4446,19 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E134" t="n">
-        <v>0.1054</v>
+        <v>0.083</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0006906698986089434</v>
+        <v>0.004124197058622408</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0111</v>
+        <v>0.0069</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1054</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="135">
@@ -4476,19 +4476,19 @@
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0094</v>
+        <v>0.027</v>
       </c>
       <c r="F135" t="n">
-        <v>0.763044251923786</v>
+        <v>0.3510859059757345</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0001</v>
+        <v>0.0007</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0094</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="136">
@@ -4506,19 +4506,19 @@
         <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>1031</v>
+        <v>1191</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.0207</v>
+        <v>-0.0183</v>
       </c>
       <c r="F136" t="n">
-        <v>0.5075873322008524</v>
+        <v>0.5289738622964122</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0207</v>
+        <v>0.0183</v>
       </c>
     </row>
     <row r="137">
@@ -4536,19 +4536,19 @@
         <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>1030</v>
+        <v>1190</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.0135</v>
+        <v>-0.0183</v>
       </c>
       <c r="F137" t="n">
-        <v>0.6653196485453993</v>
+        <v>0.5275479186688439</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0135</v>
+        <v>0.0183</v>
       </c>
     </row>
     <row r="138">
@@ -4566,19 +4566,19 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.0161</v>
+        <v>-0.0361</v>
       </c>
       <c r="F138" t="n">
-        <v>0.5349204663254319</v>
+        <v>0.1426795216244115</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0003</v>
+        <v>0.0013</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0161</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="139">
@@ -4596,19 +4596,19 @@
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0089</v>
+        <v>0.0113</v>
       </c>
       <c r="F139" t="n">
-        <v>0.7306396272319571</v>
+        <v>0.6466741961268396</v>
       </c>
       <c r="G139" t="n">
         <v>0.0001</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0089</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="140">
@@ -4626,19 +4626,19 @@
         <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.0278</v>
+        <v>-0.0183</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2852845633800963</v>
+        <v>0.4590110941540629</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0008</v>
+        <v>0.0003</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0278</v>
+        <v>0.0183</v>
       </c>
     </row>
     <row r="141">
@@ -4656,19 +4656,19 @@
         <v>3</v>
       </c>
       <c r="D141" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.0388</v>
+        <v>-0.0103</v>
       </c>
       <c r="F141" t="n">
-        <v>0.1352458884395275</v>
+        <v>0.6760199010028926</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0015</v>
+        <v>0.0001</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0388</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="142">
@@ -4686,19 +4686,19 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>1305</v>
+        <v>1465</v>
       </c>
       <c r="E142" t="n">
-        <v>0.0164</v>
+        <v>0.01</v>
       </c>
       <c r="F142" t="n">
-        <v>0.5528198018891866</v>
+        <v>0.7031190036551841</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0164</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="143">
@@ -4716,19 +4716,19 @@
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>1304</v>
+        <v>1464</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.0195</v>
+        <v>-0.0118</v>
       </c>
       <c r="F143" t="n">
-        <v>0.4813737840929934</v>
+        <v>0.6531285427524104</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0195</v>
+        <v>0.0118</v>
       </c>
     </row>
     <row r="144">
@@ -4746,19 +4746,19 @@
         <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>1303</v>
+        <v>1463</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.0135</v>
+        <v>-0.0247</v>
       </c>
       <c r="F144" t="n">
-        <v>0.6262338514474116</v>
+        <v>0.3452714729625672</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0002</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0135</v>
+        <v>0.0247</v>
       </c>
     </row>
     <row r="145">
@@ -4776,19 +4776,19 @@
         <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.0354</v>
+        <v>-0.0325</v>
       </c>
       <c r="F145" t="n">
-        <v>0.2018844474918695</v>
+        <v>0.2142447870270033</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0013</v>
+        <v>0.0011</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0354</v>
+        <v>0.0325</v>
       </c>
     </row>
     <row r="146">
@@ -4806,19 +4806,19 @@
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E146" t="n">
-        <v>0.0286</v>
+        <v>0.0387</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3032230186504039</v>
+        <v>0.1391171199324407</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0008</v>
+        <v>0.0015</v>
       </c>
       <c r="H146" t="n">
-        <v>0.0286</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="147">
@@ -4836,19 +4836,19 @@
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.0329</v>
+        <v>0.0101</v>
       </c>
       <c r="F147" t="n">
-        <v>0.2362394485374011</v>
+        <v>0.6986986386443921</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0011</v>
+        <v>0.0001</v>
       </c>
       <c r="H147" t="n">
-        <v>0.0329</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="148">
@@ -4866,19 +4866,19 @@
         <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0146</v>
+        <v>0.0311</v>
       </c>
       <c r="F148" t="n">
-        <v>0.598311164588707</v>
+        <v>0.2347948875653352</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0002</v>
+        <v>0.001</v>
       </c>
       <c r="H148" t="n">
-        <v>0.0146</v>
+        <v>0.0311</v>
       </c>
     </row>
     <row r="149">
@@ -4896,19 +4896,19 @@
         <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>1299</v>
+        <v>1459</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.0144</v>
+        <v>0.0375</v>
       </c>
       <c r="F149" t="n">
-        <v>0.6051556053055808</v>
+        <v>0.1524539756137026</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0002</v>
+        <v>0.0014</v>
       </c>
       <c r="H149" t="n">
-        <v>0.0144</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="150">
@@ -4926,19 +4926,19 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E150" t="n">
-        <v>0.1058</v>
+        <v>0.0834</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0006592361251052451</v>
+        <v>0.003937936842102352</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0112</v>
+        <v>0.007</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1058</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="151">
@@ -4956,19 +4956,19 @@
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0094</v>
+        <v>0.0272</v>
       </c>
       <c r="F151" t="n">
-        <v>0.7638041796056445</v>
+        <v>0.3473540890495826</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0001</v>
+        <v>0.0007</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0094</v>
+        <v>0.0272</v>
       </c>
     </row>
     <row r="152">
@@ -4986,19 +4986,19 @@
         <v>2</v>
       </c>
       <c r="D152" t="n">
-        <v>1031</v>
+        <v>1191</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.0206</v>
+        <v>-0.0184</v>
       </c>
       <c r="F152" t="n">
-        <v>0.5078735693908559</v>
+        <v>0.5256117978481536</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0206</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="153">
@@ -5016,19 +5016,19 @@
         <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>1030</v>
+        <v>1190</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.0142</v>
+        <v>-0.0193</v>
       </c>
       <c r="F153" t="n">
-        <v>0.6486979922433088</v>
+        <v>0.5055310193903448</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0002</v>
+        <v>0.0004</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0142</v>
+        <v>0.0193</v>
       </c>
     </row>
     <row r="154">
@@ -5046,19 +5046,19 @@
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.0158</v>
+        <v>-0.0375</v>
       </c>
       <c r="F154" t="n">
-        <v>0.5428738957439365</v>
+        <v>0.1280968137346019</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0002</v>
+        <v>0.0014</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0158</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="155">
@@ -5076,19 +5076,19 @@
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E155" t="n">
-        <v>0.0102</v>
+        <v>0.01</v>
       </c>
       <c r="F155" t="n">
-        <v>0.695149390817818</v>
+        <v>0.6865207536781721</v>
       </c>
       <c r="G155" t="n">
         <v>0.0001</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0102</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="156">
@@ -5106,19 +5106,19 @@
         <v>2</v>
       </c>
       <c r="D156" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.0198</v>
+        <v>-0.0174</v>
       </c>
       <c r="F156" t="n">
-        <v>0.4453064501225944</v>
+        <v>0.4815821994194102</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0198</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="157">
@@ -5136,19 +5136,19 @@
         <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.0339</v>
+        <v>-0.0101</v>
       </c>
       <c r="F157" t="n">
-        <v>0.1925536738761989</v>
+        <v>0.6813735020684951</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0011</v>
+        <v>0.0001</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0339</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="158">
@@ -5166,19 +5166,19 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>1305</v>
+        <v>1465</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0172</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F158" t="n">
-        <v>0.5340816382799776</v>
+        <v>0.7131506717337155</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0172</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="159">
@@ -5196,19 +5196,19 @@
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>1304</v>
+        <v>1464</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.0176</v>
+        <v>-0.0119</v>
       </c>
       <c r="F159" t="n">
-        <v>0.526022290141825</v>
+        <v>0.6502908531046107</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0176</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="160">
@@ -5226,19 +5226,19 @@
         <v>2</v>
       </c>
       <c r="D160" t="n">
-        <v>1303</v>
+        <v>1463</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.0105</v>
+        <v>-0.0248</v>
       </c>
       <c r="F160" t="n">
-        <v>0.7055444225082879</v>
+        <v>0.3424730487216813</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0105</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="161">
@@ -5256,13 +5256,13 @@
         <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E161" t="n">
         <v>-0.0329</v>
       </c>
       <c r="F161" t="n">
-        <v>0.235928739738261</v>
+        <v>0.2088586581460622</v>
       </c>
       <c r="G161" t="n">
         <v>0.0011</v>
@@ -5286,19 +5286,19 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E162" t="n">
-        <v>-0.0692</v>
+        <v>-0.0483</v>
       </c>
       <c r="F162" t="n">
-        <v>0.01247144192459296</v>
+        <v>0.06475547778253506</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0048</v>
+        <v>0.0023</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0692</v>
+        <v>0.0483</v>
       </c>
     </row>
     <row r="163">
@@ -5316,19 +5316,19 @@
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.043</v>
       </c>
       <c r="F163" t="n">
-        <v>0.01710091864962435</v>
+        <v>0.1004242175383318</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0044</v>
+        <v>0.0018</v>
       </c>
       <c r="H163" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="164">
@@ -5346,19 +5346,19 @@
         <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>1300</v>
+        <v>1460</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.0252</v>
+        <v>-0.0009</v>
       </c>
       <c r="F164" t="n">
-        <v>0.3648304868257428</v>
+        <v>0.9710689683104307</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0252</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="165">
@@ -5376,19 +5376,19 @@
         <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>1299</v>
+        <v>1459</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.0062</v>
+        <v>0.0047</v>
       </c>
       <c r="F165" t="n">
-        <v>0.8220888854415636</v>
+        <v>0.8566899824292189</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>0.0062</v>
+        <v>0.0047</v>
       </c>
     </row>
     <row r="166">
@@ -5406,19 +5406,19 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E166" t="n">
-        <v>0.005</v>
+        <v>-0.0418</v>
       </c>
       <c r="F166" t="n">
-        <v>0.8718751328553422</v>
+        <v>0.1486927246779118</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="H166" t="n">
-        <v>0.005</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="167">
@@ -5436,19 +5436,19 @@
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1032</v>
+        <v>1192</v>
       </c>
       <c r="E167" t="n">
-        <v>0.0312</v>
+        <v>0.0009</v>
       </c>
       <c r="F167" t="n">
-        <v>0.3165687024627584</v>
+        <v>0.9751574360744267</v>
       </c>
       <c r="G167" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0312</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="168">
@@ -5466,19 +5466,19 @@
         <v>2</v>
       </c>
       <c r="D168" t="n">
-        <v>1031</v>
+        <v>1191</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0511</v>
+        <v>0.0094</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1009842780890736</v>
+        <v>0.744887596681604</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0026</v>
+        <v>0.0001</v>
       </c>
       <c r="H168" t="n">
-        <v>0.0511</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="169">
@@ -5496,19 +5496,19 @@
         <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>1030</v>
+        <v>1190</v>
       </c>
       <c r="E169" t="n">
-        <v>0.0485</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F169" t="n">
-        <v>0.1197368342579016</v>
+        <v>0.7656074629473789</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0024</v>
+        <v>0.0001</v>
       </c>
       <c r="H169" t="n">
-        <v>0.0485</v>
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -5526,19 +5526,19 @@
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>1486</v>
+        <v>1646</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.0032</v>
+        <v>-0.0392</v>
       </c>
       <c r="F170" t="n">
-        <v>0.9015989330270174</v>
+        <v>0.112194354197777</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="H170" t="n">
-        <v>0.0032</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="171">
@@ -5556,19 +5556,19 @@
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>1485</v>
+        <v>1645</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.0005</v>
+        <v>-0.0281</v>
       </c>
       <c r="F171" t="n">
-        <v>0.9833650297299761</v>
+        <v>0.2548337287218819</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="H171" t="n">
-        <v>0.0005</v>
+        <v>0.0281</v>
       </c>
     </row>
     <row r="172">
@@ -5586,19 +5586,19 @@
         <v>2</v>
       </c>
       <c r="D172" t="n">
-        <v>1484</v>
+        <v>1644</v>
       </c>
       <c r="E172" t="n">
-        <v>0.0049</v>
+        <v>-0.0343</v>
       </c>
       <c r="F172" t="n">
-        <v>0.8505146015228779</v>
+        <v>0.1642831227744022</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="H172" t="n">
-        <v>0.0049</v>
+        <v>0.0343</v>
       </c>
     </row>
     <row r="173">
@@ -5616,19 +5616,19 @@
         <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>1483</v>
+        <v>1643</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0211</v>
+        <v>-0.0104</v>
       </c>
       <c r="F173" t="n">
-        <v>0.417697547406956</v>
+        <v>0.6745743419444531</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="H173" t="n">
-        <v>0.0211</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="174">
@@ -5646,19 +5646,19 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>1305</v>
+        <v>1465</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0424</v>
       </c>
       <c r="F174" t="n">
-        <v>0.7217335863368635</v>
+        <v>0.1049240829303895</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0001</v>
+        <v>0.0018</v>
       </c>
       <c r="H174" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0424</v>
       </c>
     </row>
     <row r="175">
@@ -5676,19 +5676,19 @@
         <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>1304</v>
+        <v>1464</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.0151</v>
+        <v>-0.0497</v>
       </c>
       <c r="F175" t="n">
-        <v>0.5853771554997863</v>
+        <v>0.05724121509719811</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0002</v>
+        <v>0.0025</v>
       </c>
       <c r="H175" t="n">
-        <v>0.0151</v>
+        <v>0.0497</v>
       </c>
     </row>
     <row r="176">
@@ -5706,19 +5706,19 @@
         <v>2</v>
       </c>
       <c r="D176" t="n">
-        <v>1303</v>
+        <v>1463</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.0024</v>
+        <v>-0.0366</v>
       </c>
       <c r="F176" t="n">
-        <v>0.9310217622207084</v>
+        <v>0.1618232541361478</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="H176" t="n">
-        <v>0.0024</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="177">
@@ -5736,19 +5736,19 @@
         <v>3</v>
       </c>
       <c r="D177" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E177" t="n">
-        <v>0.0044</v>
+        <v>-0.0419</v>
       </c>
       <c r="F177" t="n">
-        <v>0.8727818236374584</v>
+        <v>0.1095161234269827</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="H177" t="n">
-        <v>0.0044</v>
+        <v>0.0419</v>
       </c>
     </row>
   </sheetData>
@@ -5762,7 +5762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5822,49 +5822,49 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1302</v>
+        <v>1462</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1857</v>
+        <v>0.197</v>
       </c>
       <c r="F2" t="n">
-        <v>1.462278934836283e-11</v>
+        <v>2.975956023165638e-14</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0345</v>
+        <v>0.0388</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1857</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pct_chg</t>
+          <t>turn</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>510050.SH-510100.SH</t>
+          <t>588080.SH-588050.SH</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1300</v>
+        <v>1193</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1275</v>
+        <v>0.0835</v>
       </c>
       <c r="F3" t="n">
-        <v>4.002130915061709e-06</v>
+        <v>0.003909283436569167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0163</v>
+        <v>0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1275</v>
+        <v>0.0835</v>
       </c>
     </row>
     <row r="4">
@@ -5882,85 +5882,85 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1058</v>
+        <v>0.0834</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006592361251052451</v>
+        <v>0.003937936842102352</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0112</v>
+        <v>0.007</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1058</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>pct_chg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>588080.SH-588050.SH</t>
+          <t>510050.SH-510100.SH</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1033</v>
+        <v>1460</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1054</v>
+        <v>-0.0833</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0006906698986089434</v>
+        <v>0.001453459014690324</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0111</v>
+        <v>0.0069</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1054</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iopv</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>159915.SZ-159952.SZ</t>
+          <t>588080.SH-588050.SH</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1486</v>
+        <v>1193</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1034</v>
+        <v>0.083</v>
       </c>
       <c r="F6" t="n">
-        <v>6.525116086013564e-05</v>
+        <v>0.004124197058622408</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0107</v>
+        <v>0.0069</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1034</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>turn</t>
+          <t>amt_btin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5972,25 +5972,25 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1003</v>
+        <v>0.0795</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001244884131618857</v>
+        <v>0.005986226028564703</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0101</v>
+        <v>0.0063</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1003</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>amt_btin</t>
+          <t>amt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6002,49 +6002,49 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1033</v>
+        <v>1193</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0974</v>
+        <v>0.0791</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001725477739666054</v>
+        <v>0.006260604829910568</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0095</v>
+        <v>0.0063</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0974</v>
+        <v>0.0791</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>amt</t>
+          <t>NAV_iopv_discount</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>588080.SH-588050.SH</t>
+          <t>159915.SZ-159977.SZ</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1033</v>
+        <v>1465</v>
       </c>
       <c r="E9" t="n">
-        <v>0.097</v>
+        <v>-0.0775</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001798779041004703</v>
+        <v>0.003004213155374892</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0094</v>
+        <v>0.006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.097</v>
+        <v>0.0775</v>
       </c>
     </row>
     <row r="10">
@@ -6055,26 +6055,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>510050.SH-510100.SH</t>
+          <t>159915.SZ-159952.SZ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1301</v>
+        <v>1646</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0806</v>
+        <v>-0.0745</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003633692135525864</v>
+        <v>0.002476983822716446</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0065</v>
+        <v>0.0056</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0806</v>
+        <v>0.0745</v>
       </c>
     </row>
     <row r="11">
@@ -6089,22 +6089,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1304</v>
+        <v>1465</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.0658</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005542304151129953</v>
+        <v>0.01182197363890306</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0059</v>
+        <v>0.0043</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0658</v>
       </c>
     </row>
     <row r="12">
@@ -6115,32 +6115,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>159915.SZ-159977.SZ</t>
+          <t>588080.SH-588050.SH</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1303</v>
+        <v>1190</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0706</v>
+        <v>0.0601</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01082749214576983</v>
+        <v>0.03807197236771273</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005</v>
+        <v>0.0036</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0706</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ETF申购赎回现金差额</t>
+          <t>netinflow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6149,262 +6149,112 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1302</v>
+        <v>1461</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0692</v>
+        <v>-0.0562</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01247144192459296</v>
+        <v>0.03179241750970469</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0048</v>
+        <v>0.0032</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0692</v>
+        <v>0.0562</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>netinflow</t>
+          <t>unit_total</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>588080.SH-588050.SH</t>
+          <t>159915.SZ-159977.SZ</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1031</v>
+        <v>1473</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0664</v>
+        <v>-0.0527</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0329387044269339</v>
+        <v>0.04300037084029729</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0044</v>
+        <v>0.0028</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0664</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ETF申购赎回现金差额</t>
+          <t>pct_chg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>510050.SH-510100.SH</t>
+          <t>159915.SZ-159977.SZ</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1301</v>
+        <v>1461</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0525</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01710091864962435</v>
+        <v>0.04480930104797084</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0044</v>
+        <v>0.0028</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0525</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>netinflow</t>
+          <t>iopv</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>159915.SZ-159977.SZ</t>
+          <t>159915.SZ-159952.SZ</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1302</v>
+        <v>1646</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01713703726938595</v>
+        <v>0.04683192060403791</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0044</v>
+        <v>0.0024</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06610000000000001</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NAV_iopv_discount</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>588080.SH-588050.SH</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1031</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.0649</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.03726009446297148</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.0649</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>netinflow</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>159915.SZ-159952.SZ</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1486</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.0616</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.01758938509015766</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.0038</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.0616</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>NAV_iopv_discount</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>159915.SZ-159952.SZ</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1486</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.02068301455114766</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>pct_chg</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>510050.SH-510100.SH</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1299</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.0588</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.03396974467401923</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.0588</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>pct_chg</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>159915.SZ-159977.SZ</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1301</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.0578</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.03696788601635918</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0578</v>
+        <v>0.049</v>
       </c>
     </row>
   </sheetData>
